--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45163.60962392537</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="7" t="n"/>
       <c r="F1" s="7" t="n"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="C14" s="15" t="n"/>
       <c r="D14" s="5" t="n">
-        <v>615.005</v>
+        <v>707.256</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1" s="20">
@@ -954,7 +954,7 @@
       </c>
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>750.946</v>
+        <v>863.588</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" s="20">
@@ -970,22 +970,9 @@
       </c>
       <c r="C16" s="15" t="n"/>
       <c r="D16" s="5" t="n">
-        <v>882.258</v>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
+        <v>1014.597</v>
+      </c>
+    </row>
     <row r="30" ht="13.5" customHeight="1" s="20" thickBot="1"/>
     <row r="31" ht="14.25" customHeight="1" s="20" thickBot="1" thickTop="1">
       <c r="A31" s="16" t="inlineStr">
@@ -1000,15 +987,15 @@
     <row r="32" ht="13.5" customHeight="1" s="20" thickTop="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -987,15 +987,15 @@
     <row r="32" ht="13.5" customHeight="1" s="20" thickTop="1"/>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="7" t="n"/>
       <c r="F1" s="7" t="n"/>
@@ -987,15 +987,15 @@
     <row r="32" ht="13.5" customHeight="1" s="20" thickTop="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="7" t="n"/>
       <c r="F1" s="7" t="n"/>

--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="7" t="n"/>
       <c r="F1" s="7" t="n"/>

--- a/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
+++ b/LISTAS/ma/TORNILLOS PUNTA MECHA FLANGEADA DISMAY.xlsx
@@ -791,7 +791,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45266</v>
+        <v>45261.57777047421</v>
       </c>
       <c r="E1" s="7" t="n"/>
       <c r="F1" s="7" t="n"/>
@@ -938,7 +938,7 @@
       </c>
       <c r="C14" s="15" t="n"/>
       <c r="D14" s="5" t="n">
-        <v>707.256</v>
+        <v>984.14</v>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1" s="20">
@@ -954,7 +954,7 @@
       </c>
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>863.588</v>
+        <v>1201.68</v>
       </c>
     </row>
     <row r="16" ht="17.25" customHeight="1" s="20">
@@ -970,9 +970,22 @@
       </c>
       <c r="C16" s="15" t="n"/>
       <c r="D16" s="5" t="n">
-        <v>1014.597</v>
-      </c>
-    </row>
+        <v>1411.81</v>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30" ht="13.5" customHeight="1" s="20" thickBot="1"/>
     <row r="31" ht="14.25" customHeight="1" s="20" thickBot="1" thickTop="1">
       <c r="A31" s="16" t="inlineStr">
@@ -987,15 +1000,15 @@
     <row r="32" ht="13.5" customHeight="1" s="20" thickTop="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
